--- a/streamlit_app/arquivo_gym.xlsx
+++ b/streamlit_app/arquivo_gym.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2727,6 +2727,998 @@
         </is>
       </c>
       <c r="F72" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>cadeira extensora</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>70,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>16,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>leg press</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>180,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>elevação lateral</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>agachamento</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>elevação frontal</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>8,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>cadeira adutora</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>65,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>cruxifixo inverso</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>9,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>cadeira abdutora</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>70,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>remada alta</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>15,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>flexora em pe</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>12,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>panturrilha</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>200,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>fly inclinado</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>20,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>cruxifixo inclinado</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>14,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>fly reto</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>18,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>pullover</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>24,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>peck deck</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>55,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>triceps frances</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>16,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>tricipes corda</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>20,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>pulley triceps inverso</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>20,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>abdominal prancha</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>abdominal solo</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>puxada frente aberta</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>puxada triangulo</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>45,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>remada maquina</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>60,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>remada serrote</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>18,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>pulldown</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>22,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>rosca barra polia</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>22,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>rosca martelo</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>12,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>rosca concentrada</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>10,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>abdominal infra paralela</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
